--- a/demo/indicators_params.xlsx
+++ b/demo/indicators_params.xlsx
@@ -428,7 +428,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>5299001234567890ABCD</t>
+          <t>213800MERIDNGRPHLD42</t>
         </is>
       </c>
     </row>
